--- a/jogos_2024-10-02.xlsx
+++ b/jogos_2024-10-02.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sigma Olomouc II</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="M4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O4" t="n">
         <v>3.25</v>
       </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.88</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="Y4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['84', '86']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI4" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45567.45833333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>EGS Gafsa</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.96</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA5" t="n">
         <v>4.5</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['13', '36']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45567.45833333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,87 +1159,87 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1248,20 +1248,20 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['17', '19', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45567.45833333334</v>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varnsdorf</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.89</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.34</v>
@@ -1338,59 +1338,59 @@
         <v>2.99</v>
       </c>
       <c r="T7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['32', '36']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['66', '86']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['33', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45567.45833333334</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sigma Olomouc II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
         <v>3.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
         <v>1.03</v>
@@ -1482,38 +1482,38 @@
         <v>3.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['32', '36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['66', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AI8" t="n">
         <v>1.67</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1635,20 +1635,20 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '19', '68']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45567.45833333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EGS Gafsa</t>
+          <t>Varnsdorf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,65 +1701,65 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>3.89</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>2.45</v>
+        <v>2.99</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['13', '36']</t>
+          <t>['33', '90+3']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.5</v>
+        <v>2.63</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45567.45833333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.04</v>
+        <v>3.88</v>
       </c>
       <c r="N11" t="n">
-        <v>2.56</v>
+        <v>3.96</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.55</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>2.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['84', '86']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45567.45833333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45567.5</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Enyimba</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Akwa United</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45567.5</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>2.88</v>
+        <v>5.75</v>
       </c>
       <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45567.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Enyimba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Akwa United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,65 +2475,65 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="AA16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.44</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.15</v>
+        <v>2.34</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45567.5</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q17" t="n">
-        <v>8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.7</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>2.31</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AH17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45567.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>3.51</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45567.54166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.51</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['51', '55', '58']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI20" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45567.54166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T21" t="n">
         <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.88</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.25</v>
       </c>
-      <c r="X21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['51', '55', '58']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45567.54166666666</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>2</v>
@@ -3378,28 +3378,28 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.15</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.74</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
         <v>2.5</v>
@@ -3411,50 +3411,50 @@
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '73']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['21', '44', '48']</t>
+          <t>['23', '33', '79']</t>
         </is>
       </c>
       <c r="AG23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45567.57291666666</v>
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
@@ -3507,28 +3507,28 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>4.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.4</v>
       </c>
       <c r="T24" t="n">
         <v>2.5</v>
@@ -3540,50 +3540,50 @@
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['19', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['23', '33', '79']</t>
+          <t>['21', '44', '48']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45567.57291666666</v>
@@ -3600,35 +3600,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.75</v>
+        <v>5.24</v>
       </c>
       <c r="R25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.45</v>
       </c>
-      <c r="S25" t="n">
+      <c r="Z25" t="n">
         <v>2.55</v>
       </c>
-      <c r="T25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45567.58333333334</v>
@@ -3729,32 +3729,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="N26" t="n">
-        <v>5.03</v>
+        <v>8.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.5</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.5</v>
+        <v>1.94</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.17</v>
+        <v>1.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['16', '31']</t>
+          <t>['15', '28', '36', '75']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '67']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.02</v>
+        <v>3.92</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45567.58333333334</v>
@@ -3858,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="M27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.9</v>
       </c>
-      <c r="N27" t="n">
-        <v>4.25</v>
-      </c>
       <c r="O27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.62</v>
-      </c>
       <c r="Q27" t="n">
-        <v>5.24</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.62</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45567.58333333334</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.23</v>
+        <v>2.39</v>
       </c>
       <c r="M28" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>8.9</v>
+        <v>2.44</v>
       </c>
       <c r="O28" t="n">
-        <v>1.55</v>
+        <v>2.79</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.279999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['17', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['15', '28', '36', '75']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['50', '67']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>3.8</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45567.58333333334</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.44</v>
+        <v>5.03</v>
       </c>
       <c r="O31" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.94</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="T31" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['16', '31']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['17', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45567.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>13</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="P37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="Z37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.82</v>
       </c>
-      <c r="AA37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
+          <t>['11', '75']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG37" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.67</v>
+        <v>4.85</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45567.66666666666</v>
@@ -5287,16 +5287,16 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="M38" t="n">
+        <v>4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
         <v>3.4</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['13', '52', '75', '84']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45567.66666666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.75</v>
+        <v>1.47</v>
       </c>
       <c r="M39" t="n">
         <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>1.85</v>
+        <v>5.9</v>
       </c>
       <c r="O39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>4.75</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['45+3', '66']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['74', '90']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45567.66666666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45567.66666666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.47</v>
+        <v>2.42</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>5.9</v>
+        <v>2.63</v>
       </c>
       <c r="O41" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="P41" t="n">
         <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="R41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U41" t="n">
         <v>1.44</v>
       </c>
-      <c r="S41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="X41" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AA41" t="n">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5763,20 +5763,20 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="AJ41" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45567.66666666666</v>
@@ -5803,16 +5803,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.18</v>
+        <v>2.7</v>
       </c>
       <c r="M42" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>13</v>
+        <v>2.33</v>
       </c>
       <c r="O42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['13', '52', '75', '84']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.57</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['11', '75']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH42" t="n">
-        <v>4.85</v>
+        <v>1.43</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45567.66666666666</v>
@@ -5932,19 +5932,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -5958,55 +5958,55 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.22</v>
+        <v>3.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>2.82</v>
+        <v>1.85</v>
       </c>
       <c r="O43" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="X43" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AC43" t="n">
         <v>1.67</v>
@@ -6016,25 +6016,25 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['30', '65']</t>
+          <t>['45+3', '66']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['50', '68', '82']</t>
+          <t>['74', '90']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.64</v>
+        <v>1.2</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45567.66666666666</v>
@@ -6190,19 +6190,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.1</v>
+        <v>2.22</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>1.58</v>
+        <v>2.82</v>
       </c>
       <c r="O45" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="P45" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA45" t="n">
         <v>3.4</v>
       </c>
-      <c r="T45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y45" t="n">
+      <c r="AB45" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD45" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>['30', '65']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '68', '82']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.13</v>
+        <v>1.64</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45567.66666666666</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,109 +6319,109 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M46" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N46" t="n">
+        <v>20</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB46" t="n">
         <v>2</v>
       </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4</v>
-      </c>
-      <c r="N46" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['57', '64']</t>
+          <t>['11', '73', '83']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45567.85416666666</v>
@@ -6448,16 +6448,16 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
@@ -6466,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,55 +6474,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="M47" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="O47" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P47" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S47" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U47" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V47" t="n">
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AC47" t="n">
         <v>1.53</v>
@@ -6532,25 +6532,25 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['16', '65', '75']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['69', '90+6']</t>
+          <t>['43', '76']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45567.85416666666</v>
@@ -6577,22 +6577,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
         <v>4</v>
       </c>
-      <c r="H48" t="n">
-        <v>3</v>
-      </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.75</v>
+        <v>2.78</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>4.05</v>
+        <v>2.32</v>
       </c>
       <c r="O48" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="P48" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T48" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U48" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X48" t="n">
         <v>4</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['8', '30', '45+1', '58']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['25', '67', '90+3']</t>
+          <t>['27', '48', '69', '88']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45567.85416666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,109 +6706,109 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" t="n">
         <v>3</v>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
       <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="M49" t="n">
-        <v>9.300000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>4.05</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="Z49" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AA49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC49" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['11', '73', '83']</t>
+          <t>['8', '30', '45+1', '58']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '67', '90+3']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45567.85416666666</v>
@@ -6835,16 +6835,16 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>2</v>
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,55 +6861,55 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="M50" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N50" t="n">
-        <v>4.65</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="P50" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U50" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X50" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AC50" t="n">
         <v>1.53</v>
@@ -6919,25 +6919,25 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['16', '65', '75']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['43', '76']</t>
+          <t>['69', '90+6']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45567.85416666666</v>
@@ -6964,109 +6964,109 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
         <v>1</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M51" t="n">
         <v>4</v>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S51" t="n">
         <v>3.5</v>
       </c>
-      <c r="N51" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O51" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P51" t="n">
+      <c r="T51" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q51" t="n">
-        <v>3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U51" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V51" t="n">
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X51" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['57', '64']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['27', '48', '69', '88']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.42</v>
+        <v>2.15</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45567.85416666666</v>
@@ -7480,22 +7480,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="M55" t="n">
         <v>3.8</v>
       </c>
       <c r="N55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X55" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD55" t="n">
         <v>3.4</v>
       </c>
-      <c r="O55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S55" t="n">
-        <v>4</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X55" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '58', '90+1']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45567.9375</v>
@@ -7609,22 +7609,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="M56" t="n">
         <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P56" t="n">
         <v>2.5</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X56" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD56" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q56" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X56" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC56" t="n">
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD56" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>['50', '58', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH56" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45567.9375</v>
@@ -7867,19 +7867,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P58" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="R58" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S58" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T58" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="U58" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="V58" t="n">
         <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X58" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7956,20 +7956,20 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['14', '65', '67']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45567.97916666666</v>
@@ -8125,19 +8125,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="M60" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="O60" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P60" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S60" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T60" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="U60" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="V60" t="n">
         <v>1.01</v>
       </c>
       <c r="W60" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X60" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AD60" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8214,20 +8214,20 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['14', '65', '67']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AH60" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ60" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45567.97916666666</v>
